--- a/Sample_Data/Departments.xlsx
+++ b/Sample_Data/Departments.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="98">
   <si>
     <t>dept_ID INT</t>
   </si>
@@ -68,6 +68,243 @@
   </si>
   <si>
     <t>5th Floor Executive Suite</t>
+  </si>
+  <si>
+    <t>Cardiology</t>
+  </si>
+  <si>
+    <t>2nd Floor West Wing</t>
+  </si>
+  <si>
+    <t>Neurology</t>
+  </si>
+  <si>
+    <t>3rd Floor East Wing</t>
+  </si>
+  <si>
+    <t>Labor and Delivery</t>
+  </si>
+  <si>
+    <t>5th Floor North Wing</t>
+  </si>
+  <si>
+    <t>Orthopedics</t>
+  </si>
+  <si>
+    <t>1st Floor South Wing</t>
+  </si>
+  <si>
+    <t>General Surgery</t>
+  </si>
+  <si>
+    <t>2nd Floor Central</t>
+  </si>
+  <si>
+    <t>Psychiatry</t>
+  </si>
+  <si>
+    <t>6th Floor East Wing</t>
+  </si>
+  <si>
+    <t>Outpatient Clinic</t>
+  </si>
+  <si>
+    <t>Ground Floor North</t>
+  </si>
+  <si>
+    <t>Physical Therapy</t>
+  </si>
+  <si>
+    <t>Ground Floor South</t>
+  </si>
+  <si>
+    <t>Dermatology</t>
+  </si>
+  <si>
+    <t>4th Floor West Wing</t>
+  </si>
+  <si>
+    <t>Ophthalmology</t>
+  </si>
+  <si>
+    <t>3rd Floor North Wing</t>
+  </si>
+  <si>
+    <t>ENT (Otolaryngology)</t>
+  </si>
+  <si>
+    <t>3rd Floor South Wing</t>
+  </si>
+  <si>
+    <t>Urology</t>
+  </si>
+  <si>
+    <t>4th Floor North Wing</t>
+  </si>
+  <si>
+    <t>Gastroenterology</t>
+  </si>
+  <si>
+    <t>2nd Floor South Wing</t>
+  </si>
+  <si>
+    <t>Endocrinology</t>
+  </si>
+  <si>
+    <t>5th Floor West Wing</t>
+  </si>
+  <si>
+    <t>Pulmonology</t>
+  </si>
+  <si>
+    <t>4th Floor Central</t>
+  </si>
+  <si>
+    <t>Rheumatology</t>
+  </si>
+  <si>
+    <t>5th Floor South Wing</t>
+  </si>
+  <si>
+    <t>Nephrology</t>
+  </si>
+  <si>
+    <t>6th Floor West Wing</t>
+  </si>
+  <si>
+    <t>Infectious Disease</t>
+  </si>
+  <si>
+    <t>7th Floor North Wing</t>
+  </si>
+  <si>
+    <t>Hematology</t>
+  </si>
+  <si>
+    <t>7th Floor East Wing</t>
+  </si>
+  <si>
+    <t>Geriatrics</t>
+  </si>
+  <si>
+    <t>1st Floor West Wing</t>
+  </si>
+  <si>
+    <t>Neonatal Intensive Care Unit (NICU)</t>
+  </si>
+  <si>
+    <t>5th Floor Central</t>
+  </si>
+  <si>
+    <t>Pediatric Intensive Care Unit (PICU)</t>
+  </si>
+  <si>
+    <t>3rd Floor Central</t>
+  </si>
+  <si>
+    <t>Anesthesiology</t>
+  </si>
+  <si>
+    <t>Pathology</t>
+  </si>
+  <si>
+    <t>Basement Level 2</t>
+  </si>
+  <si>
+    <t>Blood Bank</t>
+  </si>
+  <si>
+    <t>Basement Level 1</t>
+  </si>
+  <si>
+    <t>Medical Records</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>8th Floor East Wing</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>8th Floor West Wing</t>
+  </si>
+  <si>
+    <t>Marketing and Public Relations</t>
+  </si>
+  <si>
+    <t>8th Floor North Wing</t>
+  </si>
+  <si>
+    <t>Legal and Compliance</t>
+  </si>
+  <si>
+    <t>8th Floor South Wing</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Ground Floor Central</t>
+  </si>
+  <si>
+    <t>Environmental Services (Housekeeping)</t>
+  </si>
+  <si>
+    <t>Dietary and Food Services</t>
+  </si>
+  <si>
+    <t>Ground Floor East Wing</t>
+  </si>
+  <si>
+    <t>Social Work</t>
+  </si>
+  <si>
+    <t>1st Floor East Wing</t>
+  </si>
+  <si>
+    <t>Chaplaincy / Spiritual Care</t>
+  </si>
+  <si>
+    <t>Volunteer Services</t>
+  </si>
+  <si>
+    <t>Ground Floor Main Lobby</t>
+  </si>
+  <si>
+    <t>Patient Experience</t>
+  </si>
+  <si>
+    <t>Quality and Safety</t>
+  </si>
+  <si>
+    <t>7th Floor West Wing</t>
+  </si>
+  <si>
+    <t>Research and Clinical Trials</t>
+  </si>
+  <si>
+    <t>9th Floor North Wing</t>
+  </si>
+  <si>
+    <t>Medical Library</t>
+  </si>
+  <si>
+    <t>9th Floor South Wing</t>
+  </si>
+  <si>
+    <t>Continuing Medical Education (CME)</t>
+  </si>
+  <si>
+    <t>9th Floor East Wing</t>
+  </si>
+  <si>
+    <t>Supply Chain Management</t>
+  </si>
+  <si>
+    <t>Basement Level 3</t>
   </si>
 </sst>
 </file>
@@ -438,6 +675,468 @@
         <v>18</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>33.0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>43.0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>44.0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>47.0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>48.0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>49.0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
